--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\FrenchSFcorpus\src\Ontology\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89ADAF8A-0081-4A9F-AA6D-16D94D22E25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573CA6D7-4BF1-437C-8CC6-0443CBBB0EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQ" sheetId="1" r:id="rId1"/>
@@ -1149,28 +1149,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Which characters share the same type of trait in </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>L'Homme-bicycle</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>?</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">What narrative roles are embodied in </t>
     </r>
     <r>
@@ -2428,6 +2406,28 @@
   </si>
   <si>
     <t>sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Which characters share the same traits in </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>L'Homme-bicycle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>?</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3049,7 +3049,7 @@
         <v>185</v>
       </c>
       <c r="E1" s="22" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F1" s="22" t="s">
         <v>1</v>
@@ -3066,10 +3066,10 @@
         <v>179</v>
       </c>
       <c r="D2" s="23" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F2" s="23" t="s">
         <v>221</v>
@@ -3087,10 +3087,10 @@
         <v>188</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F3" s="23" t="s">
         <v>225</v>
@@ -3108,10 +3108,10 @@
         <v>189</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>223</v>
@@ -3129,10 +3129,10 @@
         <v>219</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F5" s="23" t="s">
         <v>222</v>
@@ -3149,10 +3149,10 @@
         <v>217</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F6" s="23" t="s">
         <v>218</v>
@@ -3169,10 +3169,10 @@
         <v>203</v>
       </c>
       <c r="D7" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" s="23" t="s">
         <v>365</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>366</v>
       </c>
       <c r="F7" s="23" t="s">
         <v>220</v>
@@ -3186,16 +3186,16 @@
         <v>162</v>
       </c>
       <c r="C8" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>392</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="F8" s="23" t="s">
         <v>282</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>374</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>283</v>
       </c>
       <c r="G8" s="6"/>
     </row>
@@ -3205,16 +3205,16 @@
         <v>110</v>
       </c>
       <c r="C9" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="F9" s="23" t="s">
         <v>269</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>270</v>
       </c>
       <c r="G9" s="6"/>
     </row>
@@ -3229,10 +3229,10 @@
         <v>205</v>
       </c>
       <c r="D10" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>376</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>377</v>
       </c>
       <c r="F10" s="23" t="s">
         <v>211</v>
@@ -3249,10 +3249,10 @@
         <v>214</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F11" s="23" t="s">
         <v>213</v>
@@ -3267,10 +3267,10 @@
         <v>180</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F12" s="23" t="s">
         <v>226</v>
@@ -3286,10 +3286,10 @@
         <v>181</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>227</v>
@@ -3304,10 +3304,10 @@
         <v>186</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F14" s="23" t="s">
         <v>212</v>
@@ -3322,7 +3322,7 @@
         <v>201</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E15" s="23" t="s">
         <v>202</v>
@@ -3340,13 +3340,13 @@
         <v>207</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G16" s="6"/>
     </row>
@@ -3359,13 +3359,13 @@
         <v>209</v>
       </c>
       <c r="D17" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="E17" s="23" t="s">
         <v>399</v>
       </c>
-      <c r="E17" s="23" t="s">
-        <v>400</v>
-      </c>
       <c r="F17" s="23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G17" s="6"/>
     </row>
@@ -3380,10 +3380,10 @@
         <v>215</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>210</v>
@@ -3400,10 +3400,10 @@
         <v>228</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F19" s="23" t="s">
         <v>229</v>
@@ -3416,10 +3416,10 @@
         <v>231</v>
       </c>
       <c r="D20" s="23" t="s">
+        <v>402</v>
+      </c>
+      <c r="E20" s="23" t="s">
         <v>403</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>404</v>
       </c>
       <c r="F20" s="23" t="s">
         <v>230</v>
@@ -3432,16 +3432,16 @@
         <v>234</v>
       </c>
       <c r="D21" s="23" t="s">
+        <v>404</v>
+      </c>
+      <c r="E21" s="23" t="s">
         <v>405</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>406</v>
       </c>
       <c r="F21" s="26" t="s">
         <v>244</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -3455,10 +3455,10 @@
         <v>233</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F22" s="23" t="s">
         <v>232</v>
@@ -3468,16 +3468,16 @@
       <c r="A23" s="7"/>
       <c r="B23" s="7"/>
       <c r="C23" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D23" s="23" t="s">
+        <v>407</v>
+      </c>
+      <c r="E23" s="23" t="s">
         <v>408</v>
       </c>
-      <c r="E23" s="23" t="s">
-        <v>409</v>
-      </c>
       <c r="F23" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -3487,10 +3487,10 @@
         <v>236</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F24" s="23" t="s">
         <v>235</v>
@@ -3503,13 +3503,13 @@
         <v>237</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -3519,13 +3519,13 @@
         <v>238</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -3533,10 +3533,10 @@
         <v>246</v>
       </c>
       <c r="D27" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>414</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>415</v>
       </c>
       <c r="F27" s="23" t="s">
         <v>245</v>
@@ -3545,119 +3545,119 @@
     </row>
     <row r="28" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="23" t="s">
-        <v>247</v>
+        <v>474</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I28" s="29"/>
     </row>
     <row r="29" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F29" s="23" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G29" s="6"/>
       <c r="I29" s="29"/>
     </row>
     <row r="30" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="23" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D30" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="E30" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>419</v>
-      </c>
       <c r="F30" s="23" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I30" s="29"/>
     </row>
     <row r="31" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="23" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="F31" s="23" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G31" s="6"/>
     </row>
     <row r="32" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="23" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D32" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="E32" s="23" t="s">
         <v>421</v>
       </c>
-      <c r="E32" s="23" t="s">
-        <v>422</v>
-      </c>
       <c r="F32" s="23" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I32" s="29"/>
     </row>
     <row r="33" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D33" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>423</v>
       </c>
-      <c r="E33" s="23" t="s">
-        <v>424</v>
-      </c>
       <c r="F33" s="23" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I33" s="29"/>
     </row>
     <row r="34" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="F34" s="23" t="s">
         <v>278</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>421</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>279</v>
       </c>
       <c r="G34" s="6"/>
     </row>
     <row r="35" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="23" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D35" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="E35" s="23" t="s">
         <v>425</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>426</v>
       </c>
       <c r="F35" s="23" t="s">
         <v>239</v>
@@ -3665,41 +3665,41 @@
     </row>
     <row r="36" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="23" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F36" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="37" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="38" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="23" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F38" s="23" t="s">
         <v>240</v>
@@ -3707,10 +3707,10 @@
     </row>
     <row r="39" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="23" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E39" s="23"/>
       <c r="F39" s="23" t="s">
@@ -3719,27 +3719,27 @@
     </row>
     <row r="40" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="23" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F40" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F41" s="23" t="s">
         <v>242</v>
@@ -3747,27 +3747,27 @@
     </row>
     <row r="42" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="3:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="23" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D43" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="E43" s="23" t="s">
         <v>430</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>431</v>
       </c>
       <c r="F43" s="23" t="s">
         <v>243</v>
@@ -3775,120 +3775,120 @@
     </row>
     <row r="44" spans="3:9" ht="132" x14ac:dyDescent="0.3">
       <c r="C44" s="23" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D44" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="E44" s="23" t="s">
         <v>432</v>
       </c>
-      <c r="E44" s="23" t="s">
-        <v>433</v>
-      </c>
       <c r="F44" s="23" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="45" spans="3:9" ht="132" x14ac:dyDescent="0.3">
       <c r="C45" s="23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="46" spans="3:9" ht="92.4" x14ac:dyDescent="0.3">
       <c r="C46" s="23" t="s">
+        <v>286</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>394</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="F46" s="23" t="s">
         <v>287</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>395</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="47" spans="3:9" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="23" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="3:9" ht="79.2" x14ac:dyDescent="0.3">
       <c r="C48" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="D48" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="F48" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="D48" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="F48" s="26" t="s">
+      <c r="G48" s="6" t="s">
         <v>291</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="49" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="F49" s="23" t="s">
         <v>293</v>
-      </c>
-      <c r="D49" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="50" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="F50" s="23" t="s">
         <v>295</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="51" spans="3:7" ht="79.2" x14ac:dyDescent="0.3">
       <c r="C51" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>437</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="F51" s="23" t="s">
         <v>298</v>
-      </c>
-      <c r="D51" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="52" spans="3:7" ht="198" x14ac:dyDescent="0.3">
@@ -3896,406 +3896,406 @@
         <v>209</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E52" s="38" t="s">
+        <v>439</v>
+      </c>
+      <c r="F52" s="23" t="s">
         <v>440</v>
-      </c>
-      <c r="F52" s="23" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="53" spans="3:7" ht="184.8" x14ac:dyDescent="0.3">
       <c r="C53" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="F53" s="23" t="s">
         <v>301</v>
-      </c>
-      <c r="D53" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="F53" s="23" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="54" spans="3:7" ht="170.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>444</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="F54" s="23" t="s">
         <v>303</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>446</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="55" spans="3:7" ht="108.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="F55" s="26" t="s">
+        <v>304</v>
+      </c>
+      <c r="G55" s="6" t="s">
         <v>305</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="56" spans="3:7" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F56" s="23" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="57" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>410</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F57" s="23" t="s">
         <v>310</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="F57" s="23" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="58" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="23" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F58" s="23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="59" spans="3:7" ht="92.4" x14ac:dyDescent="0.3">
       <c r="C59" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>389</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="F59" s="23" t="s">
         <v>314</v>
-      </c>
-      <c r="D59" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="E59" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="F59" s="23" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="60" spans="3:7" ht="52.8" x14ac:dyDescent="0.3">
       <c r="C60" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="F60" s="23" t="s">
         <v>316</v>
-      </c>
-      <c r="D60" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="61" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C61" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>449</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="F61" s="23" t="s">
         <v>318</v>
-      </c>
-      <c r="D61" s="23" t="s">
-        <v>450</v>
-      </c>
-      <c r="E61" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="F61" s="23" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="62" spans="3:7" ht="303.60000000000002" x14ac:dyDescent="0.3">
       <c r="C62" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="F62" s="26" t="s">
         <v>320</v>
       </c>
-      <c r="D62" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="F62" s="26" t="s">
+      <c r="G62" s="6" t="s">
         <v>321</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="63" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="F63" s="23" t="s">
         <v>323</v>
-      </c>
-      <c r="D63" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="E63" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="64" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G64" s="6"/>
     </row>
     <row r="65" spans="3:7" ht="102" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>419</v>
+      </c>
+      <c r="F65" s="23" t="s">
         <v>326</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>455</v>
-      </c>
-      <c r="E65" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="66" spans="3:7" ht="66" x14ac:dyDescent="0.3">
       <c r="C66" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>393</v>
+      </c>
+      <c r="E66" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="F66" s="23" t="s">
         <v>328</v>
       </c>
-      <c r="D66" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>375</v>
-      </c>
-      <c r="F66" s="23" t="s">
+    </row>
+    <row r="67" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="C67" s="23" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="67" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="C67" s="23" t="s">
-        <v>330</v>
-      </c>
       <c r="D67" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="E67" s="23" t="s">
         <v>457</v>
       </c>
-      <c r="E67" s="23" t="s">
-        <v>458</v>
-      </c>
       <c r="F67" s="23" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G67" s="6"/>
     </row>
     <row r="68" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>385</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="F68" s="23" t="s">
         <v>331</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="E68" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="69" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="C69" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="E69" s="23" t="s">
+        <v>459</v>
+      </c>
+      <c r="F69" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="D69" s="23" t="s">
-        <v>459</v>
-      </c>
-      <c r="E69" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="F69" s="26" t="s">
+      <c r="G69" s="6" t="s">
         <v>334</v>
-      </c>
-      <c r="G69" s="6" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="70" spans="3:7" ht="79.2" x14ac:dyDescent="0.3">
       <c r="C70" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="F70" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="D70" s="23" t="s">
-        <v>461</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>462</v>
-      </c>
-      <c r="F70" s="26" t="s">
+      <c r="G70" s="6" t="s">
         <v>337</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="71" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="C71" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="E71" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="F71" s="23" t="s">
         <v>339</v>
-      </c>
-      <c r="D71" s="23" t="s">
-        <v>463</v>
-      </c>
-      <c r="E71" s="23" t="s">
-        <v>464</v>
-      </c>
-      <c r="F71" s="23" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="72" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="C72" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="E72" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="F72" s="23" t="s">
         <v>341</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>465</v>
-      </c>
-      <c r="E72" s="23" t="s">
-        <v>466</v>
-      </c>
-      <c r="F72" s="23" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="73" spans="3:7" ht="132" x14ac:dyDescent="0.3">
       <c r="C73" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>467</v>
+      </c>
+      <c r="F73" s="23" t="s">
         <v>343</v>
-      </c>
-      <c r="D73" s="23" t="s">
-        <v>467</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>468</v>
-      </c>
-      <c r="F73" s="23" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="74" spans="3:7" ht="171.6" x14ac:dyDescent="0.3">
       <c r="C74" s="23" t="s">
+        <v>344</v>
+      </c>
+      <c r="D74" s="23" t="s">
+        <v>468</v>
+      </c>
+      <c r="E74" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="F74" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="D74" s="23" t="s">
-        <v>469</v>
-      </c>
-      <c r="E74" s="23" t="s">
-        <v>470</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>346</v>
-      </c>
       <c r="G74" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="75" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="D75" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="E75" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="F75" s="23" t="s">
         <v>347</v>
-      </c>
-      <c r="D75" s="23" t="s">
-        <v>471</v>
-      </c>
-      <c r="E75" s="23" t="s">
-        <v>472</v>
-      </c>
-      <c r="F75" s="23" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="76" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="D76" s="23" t="s">
+        <v>413</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="F76" s="23" t="s">
         <v>349</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="E76" s="23" t="s">
-        <v>473</v>
-      </c>
-      <c r="F76" s="23" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="77" spans="3:7" ht="30.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="23" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="78" spans="3:7" ht="132" x14ac:dyDescent="0.3">
       <c r="C78" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="D78" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="E78" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="F78" s="23" t="s">
         <v>353</v>
-      </c>
-      <c r="D78" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="E78" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="F78" s="23" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="79" spans="3:7" ht="92.4" x14ac:dyDescent="0.3">
       <c r="C79" s="23" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E79" s="23"/>
       <c r="F79" s="23" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="80" spans="3:7" x14ac:dyDescent="0.3">
@@ -4634,7 +4634,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="66" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>167</v>
       </c>

--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573CA6D7-4BF1-437C-8CC6-0443CBBB0EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF33F8B9-89B2-45A0-9033-2DA2FD375AE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="CQ" sheetId="1" r:id="rId1"/>
+    <sheet name="CQs" sheetId="1" r:id="rId1"/>
     <sheet name="CQ to validate" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQ!$A$1:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">CQs!$A$1:$I$43</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="609" uniqueCount="539">
   <si>
     <t>CQ</t>
   </si>
@@ -2429,12 +2429,351 @@
       <t>?</t>
     </r>
   </si>
+  <si>
+    <t>Which novums appear in more than two works by Jules Verne?</t>
+  </si>
+  <si>
+    <t>SELECT ?novum ?label (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?novum a ?novumClass ;
+         crm:P67i_is_referred_to_by ?work .
+  FILTER(?novumClass IN (sf:H1_Conceptual_Novum, sf:H2_Concrete_Novum))
+  OPTIONAL { ?novum rdfs:label ?label . }
+}
+GROUP BY ?novum ?label
+HAVING (COUNT(DISTINCT ?work) &gt; 2)</t>
+  </si>
+  <si>
+    <t>Which types of non-human characters does Jules Verne portray?</t>
+  </si>
+  <si>
+    <t>SELECT ?type (COUNT(?char) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?char a sf:H4_Non-human_Character ;
+        gc:GP1_is_character_in ?work ;
+        crm:P2_has_type ?type .
+}
+GROUP BY ?type
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which narrative locations does Jules Verne situate outside France?</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT ?loc ?label WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?loc a gc:G13_Narrative_Location ;
+       crm:P67i_is_referred_to_by ?work ;
+       crm:P67_refers_to ?real .
+  ?real crm:P2_has_type ?locType .
+  FILTER(?locType != sf:type_france)
+  OPTIONAL { ?loc rdfs:label ?label . }
+}</t>
+  </si>
+  <si>
+    <t>type_france = devoir relier tous les lieux à des lieux supérieurs (les villes reliées à leur région, les régions à leur pays, les pays à leur continent, les continents à leur planète). Je trouve que ça fait trop</t>
+  </si>
+  <si>
+    <t>Which character archetypes does Jules Verne use most frequently?</t>
+  </si>
+  <si>
+    <t>SELECT ?archetype ?label (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?char gc:GP1_is_character_in ?work ;
+        crm:P130_shows_features_of ?archetype .
+  ?archetype a gc:G0_Character-Stoff .
+  OPTIONAL { ?archetype rdfs:label ?label . }
+}
+GROUP BY ?archetype ?label
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which Proppian functions are systematically present across Jules Verne's works?</t>
+  </si>
+  <si>
+    <t>SELECT ?function ?label (COUNT(DISTINCT ?work) AS ?nb_works)
+       (COUNT(DISTINCT ?work2) AS ?total_works) WHERE {
+  { SELECT (COUNT(DISTINCT ?w) AS ?work2) WHERE {
+      ?w a lrm:F1_Work ; dcterms:creator "Jules Verne" . } }
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?nu a gc:G9_Narrative_Unit ;
+      dlp:proper-part-of ?work ;
+      dlp:plays ?function .
+  ?function a gc:G10_Narrative_Function ;
+            crm:P2_has_type sf:type_proppian_function .
+  OPTIONAL { ?function rdfs:label ?label . }
+}
+GROUP BY ?function ?label
+HAVING (COUNT(DISTINCT ?work) = COUNT(DISTINCT ?work2))</t>
+  </si>
+  <si>
+    <t>Which types of settings does Jules Verne use most frequently?</t>
+  </si>
+  <si>
+    <t>SELECT ?type (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" ;
+        dlp:satisfied_by ?setting .
+  ?setting a gc:G12_Setting ;
+           crm:P2_has_type ?type .
+}
+GROUP BY ?type
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which narrative motifs are exclusively associated with Jules Verne's works in the corpus?</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT ?motif ?label WHERE {
+  ?motif a gc:G14_Narrative-Stoff .
+  OPTIONAL { ?motif rdfs:label ?label . }
+  FILTER EXISTS {
+    ?work crm:P130_shows_features_of ?motif ;
+          dcterms:creator "Jules Verne" .
+  }
+  FILTER NOT EXISTS {
+    ?work2 crm:P130_shows_features_of ?motif .
+    FILTER NOT EXISTS { ?work2 dcterms:creator "Jules Verne" . }
+  }
+}</t>
+  </si>
+  <si>
+    <t>Which types of novums does Jules Verne associate with scientist characters?</t>
+  </si>
+  <si>
+    <t>SELECT ?novumType (COUNT(?novum) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?char gc:GP1_is_character_in ?work ;
+        crm:P130_shows_features_of sf:Archetype_Scientist ;
+        sf:HP3_introduces_novum ?novum .
+  ?novum crm:P2_has_type ?novumType .
+}
+GROUP BY ?novumType
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>suppose un archétype scientifique</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G1_Character ; sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum ; gc:G0_Character-Stoff</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; gc:GP1_is_character_in ; crm:P130_shows_features_of ; sf:HP3_introduces_novum ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>What is the distribution of Proppian roles across Jules Verne's works?</t>
+  </si>
+  <si>
+    <t>SELECT ?role ?label (COUNT(DISTINCT ?work) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?char gc:GP1_is_character_in ?work ;
+        dlp:plays ?role .
+  ?role a gc:G11_Narrative_Role .
+  OPTIONAL { ?role rdfs:label ?label . }
+}
+GROUP BY ?role ?label
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G1_Character ; gc:G11_Narrative_Role</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; gc:GP1_is_character_in ; dlp:plays</t>
+  </si>
+  <si>
+    <t>Which psychological states are most frequent among Jules Verne's protagonists?</t>
+  </si>
+  <si>
+    <t>SELECT ?stateType ?label (COUNT(?state) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:creator "Jules Verne" .
+  ?char gc:GP1_is_character_in ?work ;
+        dlp:plays sf:Role_hero .
+  ?state a gc:G3_Psychological_State ;
+         dlp:state-of ?char ;
+         crm:P2_has_type ?stateType .
+  OPTIONAL { ?stateType rdfs:label ?label . }
+}
+GROUP BY ?stateType ?label
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; G3_Psychological_State ; G1_Character</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; dlp:plays ; dlp:state-of ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>crm:P67i_is_referred_to_by ; dcterms:creator</t>
+  </si>
+  <si>
+    <t>sf:H4_Non-human_Character ; lrm:F1_Work</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; gc:GP1_is_character_in ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G13_Narrative_Location</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; crm:P67i_is_referred_to_by ; crm:P67_refers_to ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G0_Character-Stoff</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; gc:GP1_is_character_in ; crm:P130_shows_features_of</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G9_Narrative_Unit ; gc:G10_Narrative_Function</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; dlp:proper-part-of ; dlp:plays ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; gc:G12_Setting</t>
+  </si>
+  <si>
+    <t>dcterms:creator ; dlp:satisfied_by ; crm:P2_has_type</t>
+  </si>
+  <si>
+    <t>crm:P130_shows_features_of ; dcterms:creator</t>
+  </si>
+  <si>
+    <t>In which works are novum presented as dangerous?</t>
+  </si>
+  <si>
+    <t>Suppose sf:type_catastrophe comme E55_Type pour typer les G5_Narrative_Event. Est-ce qu'on pourrait pas passer par une fonction de propp ?</t>
+  </si>
+  <si>
+    <t>SELECT DISTINCT ?work ?label WHERE {
+  ?event a gc:G5_Narrative_Event ;
+         crm:P2_has_type sf:type_catastrophe ;
+         crm:P16_used_specific_object ?novum .
+  ?novum a ?novumClass .
+  FILTER(?novumClass IN (sf:H1_Conceptual_Novum, sf:H2_Concrete_Novum))
+  ?nu a gc:G9_Narrative_Unit ;
+      crm:P67_refers_to ?event ;
+      dlp:proper-part-of ?work .
+  OPTIONAL { ?work rdfs:label ?label . }
+}</t>
+  </si>
+  <si>
+    <t>gc:G5_Narrative_Event ; sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum ; gc:G9_Narrative_Unit ; lrm:F1_Work</t>
+  </si>
+  <si>
+    <t>crm:P2_has_type ; crm:P16_used_specific_object ; crm:P67_refers_to ; dlp:proper-part-of</t>
+  </si>
+  <si>
+    <t>Which abstract novums are associated with real scientific theories?</t>
+  </si>
+  <si>
+    <t>il faudrait autoriser de relier les novum à des théories ou des objets qui existent réellement aujourd'hui</t>
+  </si>
+  <si>
+    <t>SELECT ?novum ?label ?realConcept WHERE {
+  ?novum a sf:H1_Conceptual_Novum ;
+         crm:P67_refers_to ?realConcept .
+  OPTIONAL { ?novum rdfs:label ?label . }
+}</t>
+  </si>
+  <si>
+    <t>sf:H1_Conceptual_Novum</t>
+  </si>
+  <si>
+    <t>dul:Organization</t>
+  </si>
+  <si>
+    <t>Which types of academic organizations appear in the corpus?</t>
+  </si>
+  <si>
+    <t>SELECT ?type ?label (COUNT(?org) AS ?nb) WHERE {
+  ?org a dul:Organization ;
+       crm:P2_has_type sf:type_academic_institution .
+  OPTIONAL { ?type rdfs:label ?label . }
+}
+GROUP BY ?type ?label
+ORDER BY DESC(?nb)</t>
+  </si>
+  <si>
+    <t>Which character archetypes evolved from antagonist to protagonist across different works?</t>
+  </si>
+  <si>
+    <t>What is the temporal evolution of novum types in the corpus (by decade)?</t>
+  </si>
+  <si>
+    <t>Which characters evolve from antagonist to protagonist in the same work?</t>
+  </si>
+  <si>
+    <t>SELECT ?novumType ?decade (COUNT(?novum) AS ?nb) WHERE {
+  ?work a lrm:F1_Work ;
+        dcterms:issued ?date .
+  ?novum a ?novumClass ;
+         crm:P2_has_type ?novumType ;
+         crm:P67i_is_referred_to_by ?work .
+  FILTER(?novumClass IN (sf:H1_Conceptual_Novum, sf:H2_Concrete_Novum))
+  BIND((xsd:integer(str(?date)) - (xsd:integer(str(?date)) MOD 10)) AS ?decade)
+}
+GROUP BY ?novumType ?decade
+ORDER BY ?decade ?novumType</t>
+  </si>
+  <si>
+    <t>ça signifie typer les novum</t>
+  </si>
+  <si>
+    <t>lrm:F1_Work ; sf:H1_Conceptual_Novum ; sf:H2_Concrete_Novum</t>
+  </si>
+  <si>
+    <t>dcterms:issued ; crm:P2_has_type ; crm:P67i_is_referred_to_by</t>
+  </si>
+  <si>
+    <t>SELECT ?archetype ?label WHERE {
+  ?archetype a gc:G0_Character-Stoff .
+  OPTIONAL { ?archetype rdfs:label ?label . }
+  ?char1 crm:P130_shows_features_of ?archetype ;
+         gc:GP1_is_character_in ?work1 ;
+         dlp:plays sf:Role_villain .
+  ?char2 crm:P130_shows_features_of ?archetype ;
+         gc:GP1_is_character_in ?work2 ;
+         dlp:plays sf:Role_hero .
+  FILTER(?work1 != ?work2)
+}</t>
+  </si>
+  <si>
+    <t>crm:P130_shows_features_of ; gc:GP1_is_character_in ; dlp:plays</t>
+  </si>
+  <si>
+    <t>SELECT ?char ?label ?work WHERE {
+  ?char gc:GP1_is_character_in ?work ;
+        dlp:plays ?role1 ;
+        dlp:plays ?role2 .
+  ?role1 a gc:G11_Narrative_Role ;
+         crm:P2_has_type sf:type_role_villain .
+  ?role2 a gc:G11_Narrative_Role ;
+         crm:P2_has_type sf:type_role_hero .
+  FILTER(?role1 != ?role2)
+  OPTIONAL { ?char rdfs:label ?label . }
+}</t>
+  </si>
+  <si>
+    <t>gc:G0_Character-Stoff ; lrm:F1_Work</t>
+  </si>
+  <si>
+    <t>gc:G1_Character ; lrm:F1_Work ; gc:G11_Narrative_Role</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2508,12 +2847,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Garamond"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -2636,7 +2969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2713,9 +3046,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2730,9 +3060,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3025,21 +3352,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I97"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" style="36" customWidth="1"/>
-    <col min="2" max="2" width="43.77734375" style="36" customWidth="1"/>
+    <col min="1" max="1" width="14.21875" style="35" customWidth="1"/>
+    <col min="2" max="2" width="43.77734375" style="35" customWidth="1"/>
     <col min="3" max="5" width="43.77734375" style="3" customWidth="1"/>
     <col min="6" max="6" width="52.44140625" style="3" customWidth="1"/>
     <col min="9" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="12" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="30" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="30" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="22" t="s">
@@ -3056,7 +3383,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="32">
+      <c r="A2" s="31">
         <v>1</v>
       </c>
       <c r="B2" s="25" t="s">
@@ -3077,7 +3404,7 @@
       <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="33">
+      <c r="A3" s="32">
         <v>1</v>
       </c>
       <c r="B3" s="25" t="s">
@@ -3098,7 +3425,7 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="33">
+      <c r="A4" s="32">
         <v>1</v>
       </c>
       <c r="B4" s="25" t="s">
@@ -3119,7 +3446,7 @@
       <c r="I4" s="12"/>
     </row>
     <row r="5" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="33">
+      <c r="A5" s="32">
         <v>1</v>
       </c>
       <c r="B5" s="25" t="s">
@@ -3139,7 +3466,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="33">
+      <c r="A6" s="32">
         <v>2</v>
       </c>
       <c r="B6" s="25" t="s">
@@ -3159,7 +3486,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="33">
+      <c r="A7" s="32">
         <v>2</v>
       </c>
       <c r="B7" s="25" t="s">
@@ -3179,7 +3506,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34">
+      <c r="A8" s="33">
         <v>3</v>
       </c>
       <c r="B8" s="25" t="s">
@@ -3200,7 +3527,7 @@
       <c r="G8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="33"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="25" t="s">
         <v>110</v>
       </c>
@@ -3219,7 +3546,7 @@
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="33">
+      <c r="A10" s="32">
         <v>5</v>
       </c>
       <c r="B10" s="25" t="s">
@@ -3239,7 +3566,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33">
+      <c r="A11" s="32">
         <v>5</v>
       </c>
       <c r="B11" s="25" t="s">
@@ -3278,7 +3605,7 @@
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35"/>
+      <c r="A13" s="34"/>
       <c r="B13" s="25" t="s">
         <v>117</v>
       </c>
@@ -3296,7 +3623,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="35"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="25" t="s">
         <v>184</v>
       </c>
@@ -3314,7 +3641,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="35"/>
+      <c r="A15" s="34"/>
       <c r="B15" s="25" t="s">
         <v>200</v>
       </c>
@@ -3332,7 +3659,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="35"/>
+      <c r="A16" s="34"/>
       <c r="B16" s="25" t="s">
         <v>206</v>
       </c>
@@ -3351,7 +3678,7 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="35"/>
+      <c r="A17" s="34"/>
       <c r="B17" s="25" t="s">
         <v>208</v>
       </c>
@@ -3370,7 +3697,7 @@
       <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33">
+      <c r="A18" s="32">
         <v>6</v>
       </c>
       <c r="B18" s="25" t="s">
@@ -3390,7 +3717,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33">
+      <c r="A19" s="32">
         <v>6</v>
       </c>
       <c r="B19" s="25" t="s">
@@ -3445,7 +3772,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="32">
+      <c r="A22" s="31">
         <v>6</v>
       </c>
       <c r="B22" s="25" t="s">
@@ -3895,10 +4222,10 @@
       <c r="C52" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="D52" s="38" t="s">
+      <c r="D52" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="E52" s="38" t="s">
+      <c r="E52" s="36" t="s">
         <v>439</v>
       </c>
       <c r="F52" s="23" t="s">
@@ -4108,7 +4435,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="67" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="67" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
       <c r="C67" s="23" t="s">
         <v>329</v>
       </c>
@@ -4298,68 +4625,256 @@
         <v>354</v>
       </c>
     </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C80" s="23"/>
-      <c r="D80" s="23"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="23"/>
-    </row>
-    <row r="81" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C81" s="23"/>
-      <c r="D81" s="23"/>
-      <c r="E81" s="23"/>
-      <c r="F81" s="23"/>
-    </row>
-    <row r="82" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C82" s="23"/>
-      <c r="D82" s="23"/>
-      <c r="E82" s="23"/>
-      <c r="F82" s="23"/>
-    </row>
-    <row r="83" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C83" s="30"/>
-      <c r="D83" s="30"/>
-      <c r="E83" s="30"/>
-    </row>
-    <row r="84" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C84" s="30"/>
-      <c r="D84" s="30"/>
-      <c r="E84" s="30"/>
-    </row>
-    <row r="85" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C85" s="30"/>
-      <c r="D85" s="30"/>
-      <c r="E85" s="30"/>
-    </row>
-    <row r="86" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C86" s="30"/>
-      <c r="D86" s="30"/>
-      <c r="E86" s="30"/>
-    </row>
-    <row r="87" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C87" s="30"/>
-      <c r="D87" s="30"/>
-      <c r="E87" s="30"/>
-    </row>
-    <row r="88" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C88" s="30"/>
-      <c r="D88" s="30"/>
-      <c r="E88" s="30"/>
-    </row>
-    <row r="89" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C89" s="30"/>
-      <c r="D89" s="30"/>
-      <c r="E89" s="30"/>
-    </row>
-    <row r="90" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C90" s="30"/>
-      <c r="D90" s="30"/>
-      <c r="E90" s="30"/>
-    </row>
-    <row r="91" spans="3:6" ht="23.4" x14ac:dyDescent="0.3">
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
+    <row r="80" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="C80" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="D80" s="23" t="s">
+        <v>406</v>
+      </c>
+      <c r="E80" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="F80" s="23" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="81" spans="3:7" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="C81" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="E81" s="23" t="s">
+        <v>505</v>
+      </c>
+      <c r="F81" s="23" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="82" spans="3:7" ht="132" x14ac:dyDescent="0.3">
+      <c r="C82" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="E82" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="F82" s="26" t="s">
+        <v>480</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="83" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="C83" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="F83" s="23" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="84" spans="3:7" ht="224.4" x14ac:dyDescent="0.3">
+      <c r="C84" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="D84" s="23" t="s">
+        <v>510</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="F84" s="23" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="85" spans="3:7" ht="118.8" x14ac:dyDescent="0.3">
+      <c r="C85" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="E85" s="23" t="s">
+        <v>513</v>
+      </c>
+      <c r="F85" s="23" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="86" spans="3:7" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="C86" s="23" t="s">
+        <v>488</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="E86" s="23" t="s">
+        <v>514</v>
+      </c>
+      <c r="F86" s="23" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="87" spans="3:7" ht="132" x14ac:dyDescent="0.3">
+      <c r="C87" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>493</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="F87" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="88" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="C88" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="F88" s="23" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="89" spans="3:7" ht="171.6" x14ac:dyDescent="0.3">
+      <c r="C89" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="F89" s="23" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="90" spans="3:7" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="C90" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="D90" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="E90" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="F90" s="26" t="s">
+        <v>517</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="91" spans="3:7" ht="66" x14ac:dyDescent="0.3">
+      <c r="C91" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>523</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>379</v>
+      </c>
+      <c r="F91" s="26" t="s">
+        <v>522</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="92" spans="3:7" ht="92.4" x14ac:dyDescent="0.3">
+      <c r="C92" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D92" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="E92" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="F92" s="23" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="93" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="C93" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="D93" s="23" t="s">
+        <v>537</v>
+      </c>
+      <c r="E93" s="23" t="s">
+        <v>535</v>
+      </c>
+      <c r="F93" s="23" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="94" spans="3:7" ht="145.19999999999999" x14ac:dyDescent="0.3">
+      <c r="C94" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="D94" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="E94" s="23" t="s">
+        <v>418</v>
+      </c>
+      <c r="F94" s="23" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="95" spans="3:7" ht="184.8" x14ac:dyDescent="0.3">
+      <c r="C95" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="D95" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="E95" s="23" t="s">
+        <v>533</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>530</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="96" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+      <c r="E96" s="23"/>
+      <c r="F96" s="23"/>
+    </row>
+    <row r="97" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+      <c r="E97" s="23"/>
+      <c r="F97" s="23"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H16">
@@ -4634,7 +5149,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="79.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>167</v>
       </c>

--- a/src/CQs.xlsx
+++ b/src/CQs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mathilde\Desktop\Doctorat - 2025-2028\Pipeline\SFonto\src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{205BC4A5-1638-4DD1-BE59-FDAFDE9685C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3DE00F-338B-46AC-AA4E-450865B992C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CQs" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="460">
   <si>
     <t>CQ</t>
   </si>
@@ -2806,6 +2806,41 @@
   </si>
   <si>
     <t>sf:HP7_has_facet, sf:HP8_has_valence, sf:HP9i_is_personality_of, gc:GP0_has_feature</t>
+  </si>
+  <si>
+    <t>How many stories are there on the corpus?</t>
+  </si>
+  <si>
+    <t>How many authors are represented in the data?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Who wrote </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>L'Homme-bicycle</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>How many stories are uploaded per year?</t>
   </si>
 </sst>
 </file>
@@ -3230,7 +3265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="43.77734375" style="1" customWidth="1"/>
@@ -5124,6 +5159,26 @@
         <v>447</v>
       </c>
     </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132" s="1" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133" s="1" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
